--- a/Result/profitability/6150.xlsx
+++ b/Result/profitability/6150.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2825000000000003</v>
+        <v>0.5300000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>8.498749999999999</v>
+        <v>9.744999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3912500000000003</v>
+        <v>0.6750000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>8.5625</v>
+        <v>10.1675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6475000000000003</v>
+        <v>0.7462500000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>9.338749999999999</v>
+        <v>10.47375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6362500000000003</v>
+        <v>0.6412500000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>9.17625</v>
+        <v>10.2025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.39</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5750000000000003</v>
+        <v>0.6237500000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10.07875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5175000000000003</v>
+        <v>0.4962500000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>8.96875</v>
+        <v>9.807499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5500000000000003</v>
+        <v>0.4725000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>9.188750000000001</v>
+        <v>9.51375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.5250000000000002</v>
       </c>
       <c r="N9" t="n">
-        <v>8.873750000000001</v>
+        <v>8.873749999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>0.58</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7262500000000003</v>
+        <v>0.7262500000000002</v>
       </c>
       <c r="N11" t="n">
-        <v>9.251250000000001</v>
+        <v>9.251249999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6150</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D75" t="n">
+        <v>858</v>
+      </c>
+      <c r="E75" t="n">
+        <v>169</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="G75" t="n">
+        <v>65</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.32%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>54</v>
+      </c>
+      <c r="K75" t="n">
+        <v>45</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3350000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.175000000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4025974025974026</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1879971077368041</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.04545454545454541</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.209999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.9987834549878343</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
